--- a/docs/samples/test_conges_alger.xlsx
+++ b/docs/samples/test_conges_alger.xlsx
@@ -1,52 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Conges" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conges" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -65,13 +42,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -396,320 +440,503 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22.83203125" customWidth="1"/>
-    <col min="2" max="2" width="8.83203125" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" customWidth="1"/>
-    <col min="6" max="6" width="16.83203125" customWidth="1"/>
+    <col width="22.83203125" customWidth="1" min="1" max="1"/>
+    <col width="8.83203125" customWidth="1" min="2" max="2"/>
+    <col width="8.83203125" customWidth="1" min="3" max="3"/>
+    <col width="14.83203125" customWidth="1" min="4" max="4"/>
+    <col width="14.83203125" customWidth="1" min="5" max="5"/>
+    <col width="16.83203125" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>Nom Agent</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Unité</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Atelier</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Date Début</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Date Fin</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Motif</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nom Agent</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Unité</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Atelier</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Date Début</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Date Fin</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Motif</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>Kaddour Brahim</v>
-      </c>
-      <c r="B2" t="str">
-        <v>ALG</v>
-      </c>
-      <c r="C2" t="str">
-        <v>CFA</v>
-      </c>
-      <c r="D2" t="str">
-        <v>15/02/2026</v>
-      </c>
-      <c r="E2" t="str">
-        <v>28/02/2026</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Congé annuel</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Agent 10</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ALG</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CFA</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>15/02/2026</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>28/02/2026</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Congé annuel</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>Benali Yacine</v>
-      </c>
-      <c r="B3" t="str">
-        <v>ALG</v>
-      </c>
-      <c r="C3" t="str">
-        <v>CFA</v>
-      </c>
-      <c r="D3" t="str">
-        <v>01/03/2026</v>
-      </c>
-      <c r="E3" t="str">
-        <v>15/03/2026</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Congé annuel</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Agent 04</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ALG</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CFA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>01/03/2026</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Congé annuel</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>Amrani Sofiane</v>
-      </c>
-      <c r="B4" t="str">
-        <v>ALG</v>
-      </c>
-      <c r="C4" t="str">
-        <v>CFO</v>
-      </c>
-      <c r="D4" t="str">
-        <v>10/04/2026</v>
-      </c>
-      <c r="E4" t="str">
-        <v>24/04/2026</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Congé annuel</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Agent 01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ALG</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CFO</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Congé annuel</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>Mebarki Ahmed</v>
-      </c>
-      <c r="B5" t="str">
-        <v>ALG</v>
-      </c>
-      <c r="C5" t="str">
-        <v>VOIE</v>
-      </c>
-      <c r="D5" t="str">
-        <v>05/05/2026</v>
-      </c>
-      <c r="E5" t="str">
-        <v>19/05/2026</v>
-      </c>
-      <c r="F5" t="str">
-        <v>Congé annuel</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Agent 12</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ALG</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>VOIE</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Congé annuel</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
-        <v>Boudiaf Tarek</v>
-      </c>
-      <c r="B6" t="str">
-        <v>ALG</v>
-      </c>
-      <c r="C6" t="str">
-        <v>VOIE</v>
-      </c>
-      <c r="D6" t="str">
-        <v>01/06/2026</v>
-      </c>
-      <c r="E6" t="str">
-        <v>18/06/2026</v>
-      </c>
-      <c r="F6" t="str">
-        <v>Congé annuel</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Agent 07</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ALG</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>VOIE</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Congé annuel</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="str">
-        <v>Mansouri Hocine</v>
-      </c>
-      <c r="B7" t="str">
-        <v>ALG</v>
-      </c>
-      <c r="C7" t="str">
-        <v>VOIE</v>
-      </c>
-      <c r="D7" t="str">
-        <v>15/06/2026</v>
-      </c>
-      <c r="E7" t="str">
-        <v>30/06/2026</v>
-      </c>
-      <c r="F7" t="str">
-        <v>Congé annuel</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Agent 11</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ALG</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>VOIE</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Congé annuel</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="str">
-        <v>Zeroual Noureddine</v>
-      </c>
-      <c r="B8" t="str">
-        <v>ALG</v>
-      </c>
-      <c r="C8" t="str">
-        <v>LAC</v>
-      </c>
-      <c r="D8" t="str">
-        <v>01/07/2026</v>
-      </c>
-      <c r="E8" t="str">
-        <v>21/07/2026</v>
-      </c>
-      <c r="F8" t="str">
-        <v>Congé annuel</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Agent 14</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ALG</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Congé annuel</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="str">
-        <v>Benmoussa Farid</v>
-      </c>
-      <c r="B9" t="str">
-        <v>ALG</v>
-      </c>
-      <c r="C9" t="str">
-        <v>LAC</v>
-      </c>
-      <c r="D9" t="str">
-        <v>10/07/2026</v>
-      </c>
-      <c r="E9" t="str">
-        <v>24/07/2026</v>
-      </c>
-      <c r="F9" t="str">
-        <v>Congé annuel</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Agent 05</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ALG</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Congé annuel</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="str">
-        <v>Berkane Youcef</v>
-      </c>
-      <c r="B10" t="str">
-        <v>ALG</v>
-      </c>
-      <c r="C10" t="str">
-        <v>BO</v>
-      </c>
-      <c r="D10" t="str">
-        <v>01/08/2026</v>
-      </c>
-      <c r="E10" t="str">
-        <v>15/08/2026</v>
-      </c>
-      <c r="F10" t="str">
-        <v>Congé annuel</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Agent 06</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ALG</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Congé annuel</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="str">
-        <v>Merad Mourad</v>
-      </c>
-      <c r="B11" t="str">
-        <v>ALG</v>
-      </c>
-      <c r="C11" t="str">
-        <v>BIL</v>
-      </c>
-      <c r="D11" t="str">
-        <v>15/08/2026</v>
-      </c>
-      <c r="E11" t="str">
-        <v>31/08/2026</v>
-      </c>
-      <c r="F11" t="str">
-        <v>Congé annuel</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Agent 13</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ALG</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BIL</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Congé annuel</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="str">
-        <v>Bouzid Khaled</v>
-      </c>
-      <c r="B12" t="str">
-        <v>ALG</v>
-      </c>
-      <c r="C12" t="str">
-        <v>BIL</v>
-      </c>
-      <c r="D12" t="str">
-        <v>01/09/2026</v>
-      </c>
-      <c r="E12" t="str">
-        <v>14/09/2026</v>
-      </c>
-      <c r="F12" t="str">
-        <v>Congé annuel</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Agent 08</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ALG</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BIL</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Congé annuel</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="str">
-        <v>Hadji Karim</v>
-      </c>
-      <c r="B13" t="str">
-        <v>ALG</v>
-      </c>
-      <c r="C13" t="str">
-        <v>MR</v>
-      </c>
-      <c r="D13" t="str">
-        <v>20/09/2026</v>
-      </c>
-      <c r="E13" t="str">
-        <v>10/10/2026</v>
-      </c>
-      <c r="F13" t="str">
-        <v>Congé annuel</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Agent 09</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ALG</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>10/10/2026</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Congé annuel</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="str">
-        <v>Benaissa Walid</v>
-      </c>
-      <c r="B14" t="str">
-        <v>ALG</v>
-      </c>
-      <c r="C14" t="str">
-        <v>MR</v>
-      </c>
-      <c r="D14" t="str">
-        <v>15/10/2026</v>
-      </c>
-      <c r="E14" t="str">
-        <v>28/10/2026</v>
-      </c>
-      <c r="F14" t="str">
-        <v>Congé annuel</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Agent 03</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ALG</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Congé annuel</t>
+        </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="str">
-        <v>Belkacem Omar</v>
-      </c>
-      <c r="B15" t="str">
-        <v>ALG</v>
-      </c>
-      <c r="C15" t="str">
-        <v>MR</v>
-      </c>
-      <c r="D15" t="str">
-        <v>01/11/2026</v>
-      </c>
-      <c r="E15" t="str">
-        <v>15/11/2026</v>
-      </c>
-      <c r="F15" t="str">
-        <v>Congé annuel</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Agent 02</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ALG</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>01/11/2026</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>15/11/2026</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Congé annuel</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F15"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>